--- a/locais.xlsx
+++ b/locais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arman\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568004F0-076A-4F19-93D7-98ADB851E98B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FEEB432-8A83-40B2-AC2E-35219AE90F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="204">
   <si>
     <t>categoria</t>
   </si>
@@ -370,47 +370,12 @@
     <t>64 Rue Colbert, 37000 Tours, França</t>
   </si>
   <si>
-    <r>
-      <t>Horário: Terça a Sábado, 12:00–14:00, 19:00–22:00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>; https://www.facebook.com/creperiebilien</t>
-    </r>
+    <t>Horário: Terça a Sábado, 12:00–14:00, 19:00–22:00</t>
   </si>
   <si>
     <t>Le Comptoir de Mamie Bigoude Tours Centre</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Horário: 11:30–22:00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>; https://comptoirmamiebigoude.com/carte-galettes-mamie-bigoude</t>
-    </r>
-  </si>
-  <si>
     <t>22 Rue de Châteauneuf, 37000 Tours, França</t>
   </si>
   <si>
@@ -420,143 +385,370 @@
     <t>153 Rue de la Fuye, 37000 Tours, França</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Horário: terça a domingo, 11:00–14:00, 18:30–21:30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>; https://www.instagram.com/pizza_me37/</t>
-    </r>
-  </si>
-  <si>
     <t>Noah Pâtisserie végétale</t>
   </si>
   <si>
     <t>62 Rue Colbert, 37000 Tours, França</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Horário: terça a domingo, 09:00–19:00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>; https://www.noahpatisserie.fr/</t>
-    </r>
-  </si>
-  <si>
     <t>Crêpe Touch Tours</t>
   </si>
   <si>
     <t>31 Rue de Bordeaux, 37000 Tours, França</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Horário: 10:00–22:30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>; https://restaurants.crepetouch.com/tours-centre/?utm_source=google&amp;utm_medium=organic&amp;utm_campaign=mybusiness-website</t>
-    </r>
-  </si>
-  <si>
     <t>La Bigouden</t>
   </si>
   <si>
     <t>3 Rue du Grand Marché, 37000 Tours, França</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Horário: terça a domingo, 12:00–14:00, 19:00–22:30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>; https://www.instagram.com/labigoudenofficiel/?utm_source=gmb</t>
-    </r>
-  </si>
-  <si>
     <t>smAak Natural Food</t>
   </si>
   <si>
     <t>35 Rue du Grand Marché, 37000 Tours, França</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">Horário: 11:30–14:30, 18:30–22:00; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>https://smaak-natural-food.com/index.php/menu-smaakscandinavianfood/</t>
-    </r>
+    <t>Carrefour City</t>
+  </si>
+  <si>
+    <t>Supermercado</t>
+  </si>
+  <si>
+    <t>supermarket.png</t>
+  </si>
+  <si>
+    <t>Horário: 07:00–22:00</t>
+  </si>
+  <si>
+    <t>Horário: 11:30–14:30, 18:30–22:00</t>
+  </si>
+  <si>
+    <t>Horário: terça a domingo, 12:00–14:00, 19:00–22:30</t>
+  </si>
+  <si>
+    <t>Horário: 10:00–22:30</t>
+  </si>
+  <si>
+    <t>Horário: terça a domingo, 09:00–19:00</t>
+  </si>
+  <si>
+    <t>Horário: terça a domingo, 11:00–14:00, 18:30–21:30</t>
+  </si>
+  <si>
+    <t>Horário: 11:30–22:00</t>
+  </si>
+  <si>
+    <t>118 Rue de la Fuye, 37000 Tours, França</t>
+  </si>
+  <si>
+    <t>Carrefour city Tours HERPIN</t>
+  </si>
+  <si>
+    <t>7 Rue du Dr Herpin, 37000 Tours, França</t>
+  </si>
+  <si>
+    <t>Carrefour Express</t>
+  </si>
+  <si>
+    <t>78 Rue Colbert, 37000 Tours, França</t>
+  </si>
+  <si>
+    <t>Horário: 08:00–21:00</t>
+  </si>
+  <si>
+    <t>107 Rue des Halles, 37000 Tours, França</t>
+  </si>
+  <si>
+    <t>Horário: 06:00–22:00</t>
+  </si>
+  <si>
+    <t>26 Rue Néricault Destouches, 37000 Tours, França</t>
+  </si>
+  <si>
+    <t>74 Av. de Grammont, 37000 Tours, França</t>
+  </si>
+  <si>
+    <t>Centre Commercial Les Atlantes</t>
+  </si>
+  <si>
+    <t>bolsas.png</t>
+  </si>
+  <si>
+    <t>Av. Jacques Duclos, 37700 Saint-Pierre-des-Corps, França</t>
+  </si>
+  <si>
+    <t>Horário: segunda à sábado: 09:30–20:00</t>
+  </si>
+  <si>
+    <t>Shopping</t>
+  </si>
+  <si>
+    <t>TOURS CENTRE</t>
+  </si>
+  <si>
+    <t>Horário: segunda à sábado: 10:00–19:00</t>
+  </si>
+  <si>
+    <t>19 Pl. Jean Jaurès, 37000 Tours, França</t>
+  </si>
+  <si>
+    <t>Saint-Pierre-des-Corps</t>
+  </si>
+  <si>
+    <t>Estação de Trem</t>
+  </si>
+  <si>
+    <t>67 Rue Fabienne Landy, 37700 Saint-Pierre-des-Corps, França</t>
+  </si>
+  <si>
+    <t>Auchan Supermarché Tours Galerie Palais</t>
+  </si>
+  <si>
+    <t>Horário: 08:45–21:00</t>
+  </si>
+  <si>
+    <t>Monoprix</t>
+  </si>
+  <si>
+    <t>63-65 Rue Nationale, 37000 Tours, França</t>
+  </si>
+  <si>
+    <t>Horário: 09:00–20:45</t>
+  </si>
+  <si>
+    <t>Carrefour Market Tours La Riche</t>
+  </si>
+  <si>
+    <t>13-17 Rue Du 501eme Ri, 37000 Tours, França</t>
+  </si>
+  <si>
+    <t>Horário: 08:30–20:00</t>
+  </si>
+  <si>
+    <t>Lidl</t>
+  </si>
+  <si>
+    <t>Horário: 08:30–19:30</t>
+  </si>
+  <si>
+    <t>Rue du 11 Novembre 1918, 37520 La Riche, França</t>
+  </si>
+  <si>
+    <t>19 bis Av. du Général de Gaulle, 37000 Tours, França</t>
+  </si>
+  <si>
+    <t>Place Maurice Thorez, 37700 Saint-Pierre-des-Corps, França</t>
+  </si>
+  <si>
+    <t>Horário: 08:00–20:00</t>
+  </si>
+  <si>
+    <t>MASSY TGV</t>
+  </si>
+  <si>
+    <t>38 Av. Carnot, 91300 Massy, França</t>
+  </si>
+  <si>
+    <t>Chegada: 07:25</t>
+  </si>
+  <si>
+    <t>Saída para Paris: 06:27; Retorno: 01:53</t>
+  </si>
+  <si>
+    <t>Saída para Tours: 23h28</t>
+  </si>
+  <si>
+    <t>75013 Paris, França</t>
+  </si>
+  <si>
+    <t>Torre Eifell</t>
+  </si>
+  <si>
+    <t>5 Av. Anatole France, 75007 Paris, França</t>
+  </si>
+  <si>
+    <t>Notre Daime</t>
+  </si>
+  <si>
+    <t>6 Parvis Notre-Dame - Pl. Jean-Paul II, 75004 Paris, França</t>
+  </si>
+  <si>
+    <t>Paris Austerlitz</t>
+  </si>
+  <si>
+    <t>paris</t>
+  </si>
+  <si>
+    <t>Museu do Louvre</t>
+  </si>
+  <si>
+    <t>75001 Paris, França</t>
+  </si>
+  <si>
+    <t>3 Bd des Capucines, 75002 Paris, França</t>
+  </si>
+  <si>
+    <t>Interior muito bonito</t>
+  </si>
+  <si>
+    <t>Starbucks</t>
+  </si>
+  <si>
+    <t>Pl. Charles de Gaulle, 75008 Paris, França</t>
+  </si>
+  <si>
+    <t>Arco do Triunfo</t>
+  </si>
+  <si>
+    <t>Champs-Élysées</t>
+  </si>
+  <si>
+    <t>Trocadéro</t>
+  </si>
+  <si>
+    <t>Pl. du Trocadéro et du 11 Novembre, 75016 Paris, França</t>
+  </si>
+  <si>
+    <t>Place le la Concorde</t>
+  </si>
+  <si>
+    <t>75008 Paris, França</t>
+  </si>
+  <si>
+    <t>Horário: 07:00–23:00</t>
+  </si>
+  <si>
+    <t>6 Rue Beaubourg, 75004 Paris, França</t>
+  </si>
+  <si>
+    <t>43 Rue de Richelieu, 75001 Paris, França</t>
+  </si>
+  <si>
+    <t>205 Rue Saint-Honoré, 75001 Paris, França</t>
+  </si>
+  <si>
+    <t>7 Rue de Caumartin, 75009 Paris, França</t>
+  </si>
+  <si>
+    <t>35 Rue de Ponthieu, 75008 Paris, França</t>
+  </si>
+  <si>
+    <t>6 Rue Saint-Didier, 75016 Paris, França</t>
+  </si>
+  <si>
+    <t>42 Av. de la Motte-Picquet, 75007 Paris, França</t>
+  </si>
+  <si>
+    <t>84 Rue Saint-Dominique, 75007 Paris, França</t>
+  </si>
+  <si>
+    <t>Intermarché Paris Saint Michel</t>
+  </si>
+  <si>
+    <t>Horário: 08:00–22:00</t>
+  </si>
+  <si>
+    <t>9 Bd Saint-Michel, 75005 Paris, França</t>
+  </si>
+  <si>
+    <t>Intermarché EXPRESS Paris 01</t>
+  </si>
+  <si>
+    <t>Horário: 08:30–22:00</t>
+  </si>
+  <si>
+    <t>11 Bd de Sébastopol, 75001 Paris, França</t>
+  </si>
+  <si>
+    <t>Intermarché EXPRESS Paris</t>
+  </si>
+  <si>
+    <t>107 Av. de la Bourdonnais, 75007 Paris, França</t>
+  </si>
+  <si>
+    <t>Horário: 07:30–22:00</t>
+  </si>
+  <si>
+    <t>24 Bd Saint-Michel, 75006 Paris, França</t>
+  </si>
+  <si>
+    <t>Horário: 08:00–21:45</t>
+  </si>
+  <si>
+    <t>23 Av. de l'Opéra, 75001 Paris, França</t>
+  </si>
+  <si>
+    <t>La Petite Bouclerie</t>
+  </si>
+  <si>
+    <t>33 Rue de la Harpe, 75005 Paris, França</t>
+  </si>
+  <si>
+    <t>Horário: 11:00–00:00</t>
+  </si>
+  <si>
+    <t>La Crème de Paris Notre-Dame</t>
+  </si>
+  <si>
+    <t>1 Quai Saint-Michel, 75005 Paris, França</t>
+  </si>
+  <si>
+    <t>Horário: 08:00–01:30</t>
+  </si>
+  <si>
+    <t>Cococo Japanese Bento</t>
+  </si>
+  <si>
+    <t>35 Rue Coquillière, 75001 Paris, França</t>
+  </si>
+  <si>
+    <t>Horário: 12:00–15:30</t>
+  </si>
+  <si>
+    <t>Tasca</t>
+  </si>
+  <si>
+    <t>Horário: 12:00–22:30</t>
+  </si>
+  <si>
+    <t>46 Av. de Suffren, 75015 Paris, França</t>
+  </si>
+  <si>
+    <t>Bir-Hakeim</t>
+  </si>
+  <si>
+    <t>75015 Paris, França</t>
+  </si>
+  <si>
+    <t>Pegar a linha verde C para o Paris Austerlitz</t>
+  </si>
+  <si>
+    <t>Quai de la Gare</t>
+  </si>
+  <si>
+    <t>Franprix</t>
+  </si>
+  <si>
+    <t>2 Rue Domat, 75005 Paris, França</t>
+  </si>
+  <si>
+    <t>Horário: 07:30–21:30</t>
+  </si>
+  <si>
+    <t>Horário: 07:30–22:45</t>
+  </si>
+  <si>
+    <t>165 Rue Saint-Honoré, 75001 Paris, França</t>
+  </si>
+  <si>
+    <t>Horário: 07:30–22:30</t>
+  </si>
+  <si>
+    <t>33 Rue Marbeuf, 75008 Paris, França</t>
+  </si>
+  <si>
+    <t>34 Av. de Suffren, 75015 Paris, França</t>
   </si>
 </sst>
 </file>
@@ -857,16 +1049,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J928"/>
+  <dimension ref="A1:J927"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.44140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="31.44140625" style="2" customWidth="1"/>
     <col min="3" max="3" width="21" style="2" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="15.6640625" style="2" customWidth="1"/>
     <col min="6" max="6" width="28.88671875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="189" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" style="2" customWidth="1"/>
     <col min="8" max="8" width="8.6640625" style="2" customWidth="1"/>
     <col min="9" max="9" width="21.5546875" style="2" customWidth="1"/>
     <col min="10" max="26" width="8.6640625" style="2" customWidth="1"/>
@@ -1320,7 +1512,7 @@
       <c r="F20" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="6" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1364,10 +1556,10 @@
         <v>75</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G22" s="2" t="s">
         <v>79</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1375,7 +1567,7 @@
         <v>74</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C23" s="2">
         <v>47.384902996420003</v>
@@ -1387,10 +1579,10 @@
         <v>75</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1398,7 +1590,7 @@
         <v>74</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C24" s="2">
         <v>47.396097194034802</v>
@@ -1410,10 +1602,10 @@
         <v>75</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1421,7 +1613,7 @@
         <v>74</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C25" s="2">
         <v>47.390240873824702</v>
@@ -1433,10 +1625,10 @@
         <v>75</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1444,7 +1636,7 @@
         <v>74</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C26" s="2">
         <v>47.394421899863801</v>
@@ -1456,10 +1648,10 @@
         <v>75</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1467,7 +1659,7 @@
         <v>74</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C27" s="2">
         <v>47.394345722132101</v>
@@ -1479,65 +1671,1218 @@
         <v>75</v>
       </c>
       <c r="F27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G27" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    </row>
+    <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="2">
+        <v>47.387840382417302</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0.70322010811854796</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" s="2">
+        <v>47.388472774749097</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0.698887100555731</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="2">
+        <v>47.396380579984402</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0.68986402767478505</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" s="2">
+        <v>47.392654436577303</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0.68544558708198799</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="2">
+        <v>47.392510922836102</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0.68540705748655695</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" s="2">
+        <v>47.384321303438298</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0.69169537156410799</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C34" s="2">
+        <v>47.379540427129697</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0.71499437404116795</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C35" s="2">
+        <v>47.388666568176703</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0.68935198839955303</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C36" s="2">
+        <v>47.386112808216801</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0.72375523156997601</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C37" s="2">
+        <v>47.389683915972803</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0.68843111563579396</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C38" s="2">
+        <v>47.394039725386499</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0.68708219108565105</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C39" s="2">
+        <v>47.395794055662201</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0.66751115392703797</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C40" s="2">
+        <v>47.390559281260998</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0.65909401027704295</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C41" s="2">
+        <v>47.381355358754298</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0.69530688776237104</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C42" s="2">
+        <v>47.390776218636702</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0.72003715295993798</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" s="2">
+        <v>47.386096099574097</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0.68337313544856004</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" s="2">
+        <v>48.726014490487898</v>
+      </c>
+      <c r="D44" s="2">
+        <v>2.26138776454144</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C45" s="2">
+        <v>48.858513981162801</v>
+      </c>
+      <c r="D45" s="2">
+        <v>2.2945633786699</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C46" s="2">
+        <v>48.853204736689797</v>
+      </c>
+      <c r="D46" s="2">
+        <v>2.3498919294168501</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C47" s="2">
+        <v>48.842213649455601</v>
+      </c>
+      <c r="D47" s="2">
+        <v>2.3679672585834699</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C48" s="2">
+        <v>48.861080067252502</v>
+      </c>
+      <c r="D48" s="2">
+        <v>2.3375270598039402</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C49" s="2">
+        <v>48.871902733098203</v>
+      </c>
+      <c r="D49" s="2">
+        <v>2.3337470974475298</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C50" s="2">
+        <v>48.875176996242899</v>
+      </c>
+      <c r="D50" s="2">
+        <v>2.2950372327420898</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C51" s="2">
+        <v>48.866828089800201</v>
+      </c>
+      <c r="D51" s="2">
+        <v>2.3101717088609202</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C52" s="2">
+        <v>48.864156282808601</v>
+      </c>
+      <c r="D52" s="2">
+        <v>2.2875711928928202</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C53" s="2">
+        <v>48.866438356943803</v>
+      </c>
+      <c r="D53" s="2">
+        <v>2.3210612158246899</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C54" s="2">
+        <v>48.861923891092502</v>
+      </c>
+      <c r="D54" s="2">
+        <v>2.3533037596324502</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" s="2">
+        <v>48.867693321962697</v>
+      </c>
+      <c r="D55" s="2">
+        <v>2.3366026191593101</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C56" s="2">
+        <v>48.8678075061908</v>
+      </c>
+      <c r="D56" s="2">
+        <v>2.3319670236838399</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C57" s="2">
+        <v>48.8721353475946</v>
+      </c>
+      <c r="D57" s="2">
+        <v>2.3277995704002898</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C58" s="2">
+        <v>48.872009844263502</v>
+      </c>
+      <c r="D58" s="2">
+        <v>2.30787645038777</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C59" s="2">
+        <v>48.867396991537497</v>
+      </c>
+      <c r="D59" s="2">
+        <v>2.28830365259968</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C60" s="2">
+        <v>48.855288505275198</v>
+      </c>
+      <c r="D60" s="2">
+        <v>2.30605725799419</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C61" s="2">
+        <v>48.860455292791301</v>
+      </c>
+      <c r="D61" s="2">
+        <v>2.3072506450714898</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C62" s="2">
+        <v>48.852711938374</v>
+      </c>
+      <c r="D62" s="2">
+        <v>2.3441734492746198</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C63" s="2">
+        <v>48.8596015950978</v>
+      </c>
+      <c r="D63" s="2">
+        <v>2.3483370164269601</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C64" s="2">
+        <v>48.855608600911602</v>
+      </c>
+      <c r="D64" s="2">
+        <v>2.3042669005823999</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C65" s="2">
+        <v>48.852035662443399</v>
+      </c>
+      <c r="D65" s="2">
+        <v>2.3427284359591898</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C66" s="2">
+        <v>48.867339811936098</v>
+      </c>
+      <c r="D66" s="2">
+        <v>2.3334618056774001</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C67" s="2">
+        <v>48.852786067245603</v>
+      </c>
+      <c r="D67" s="2">
+        <v>2.3442554019082502</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C68" s="2">
+        <v>48.853329736877797</v>
+      </c>
+      <c r="D68" s="2">
+        <v>2.3464503920931299</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C69" s="2">
+        <v>48.864514704841497</v>
+      </c>
+      <c r="D69" s="2">
+        <v>2.34108268279003</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C70" s="2">
+        <v>48.853863109085999</v>
+      </c>
+      <c r="D70" s="2">
+        <v>2.29660140784739</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C71" s="2">
+        <v>48.854007409440001</v>
+      </c>
+      <c r="D71" s="2">
+        <v>2.28921680478263</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C72" s="2">
+        <v>48.837061646848603</v>
+      </c>
+      <c r="D72" s="2">
+        <v>2.3727742453623901</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C73" s="2">
+        <v>48.851654440930197</v>
+      </c>
+      <c r="D73" s="2">
+        <v>2.3478139190429101</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C74" s="2">
+        <v>48.863964398668401</v>
+      </c>
+      <c r="D74" s="2">
+        <v>2.33442905569505</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C75" s="2">
+        <v>48.871321510497097</v>
+      </c>
+      <c r="D75" s="2">
+        <v>2.30420784055993</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C76" s="2">
+        <v>48.855967140591801</v>
+      </c>
+      <c r="D76" s="2">
+        <v>2.2949297558487198</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="78" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="80" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -2385,7 +3730,6 @@
     <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/locais.xlsx
+++ b/locais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arman\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FEEB432-8A83-40B2-AC2E-35219AE90F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517A62CB-CA1E-49FF-A7FF-F5C7155A1BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="208">
   <si>
     <t>categoria</t>
   </si>
@@ -749,6 +749,18 @@
   </si>
   <si>
     <t>34 Av. de Suffren, 75015 Paris, França</t>
+  </si>
+  <si>
+    <t>The LEGO® Store Paris Les Halles</t>
+  </si>
+  <si>
+    <t>1 Pass. de la Canopée, 75001 Paris, França</t>
+  </si>
+  <si>
+    <t>lego.png</t>
+  </si>
+  <si>
+    <t>Loja LEGO</t>
   </si>
 </sst>
 </file>
@@ -2879,7 +2891,32 @@
         <v>146</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C77" s="2">
+        <v>48.8632227508607</v>
+      </c>
+      <c r="D77" s="2">
+        <v>2.3486028944285802</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
     <row r="78" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="79" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="80" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
